--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B4" t="n">
-        <v>57324</v>
+        <v>90549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,35 +922,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,22 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +997,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B5" t="n">
-        <v>90549</v>
+        <v>57324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,30 +1032,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,12 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1122,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>119697323</v>
       </c>
       <c r="B4" t="n">
-        <v>90549</v>
+        <v>90559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B4" t="n">
-        <v>90559</v>
+        <v>57329</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,30 +922,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,12 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>57324</v>
+        <v>90571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1046,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,22 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,6 +1121,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>90571</v>
+        <v>90575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -924,11 +924,6 @@
       <c r="E4" t="n">
         <v>102621</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sparvuggla</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Glaucidium passerinum</t>
@@ -1033,7 +1028,7 @@
         <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>90575</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,11 +1042,6 @@
       </c>
       <c r="E5" t="n">
         <v>3215</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B4" t="n">
-        <v>57329</v>
+        <v>90593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,22 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,6 +997,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1032,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>102621</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1097,12 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1122,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B4" t="n">
-        <v>90593</v>
+        <v>57333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,30 +922,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,12 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>57333</v>
+        <v>90606</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1046,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,22 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,6 +1121,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>90606</v>
+        <v>90605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B4" t="n">
-        <v>57333</v>
+        <v>90605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,35 +922,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,22 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +997,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B5" t="n">
-        <v>90605</v>
+        <v>57333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,30 +1032,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,12 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1122,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B4" t="n">
-        <v>90605</v>
+        <v>57333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,30 +922,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,12 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B5" t="n">
-        <v>57333</v>
+        <v>90605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1046,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,22 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,6 +1121,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122272418</v>
+        <v>119697323</v>
       </c>
       <c r="B4" t="n">
-        <v>57333</v>
+        <v>90606</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,35 +922,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,22 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +997,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119697323</v>
+        <v>122272418</v>
       </c>
       <c r="B5" t="n">
-        <v>90605</v>
+        <v>57334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,30 +1032,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,12 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1122,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45153-2023 artfynd.xlsx
+++ b/artfynd/A 45153-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112510635</v>
+        <v>119697323</v>
       </c>
       <c r="B2" t="n">
-        <v>102356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Livvika, Dånsjön, Forsa, Hls</t>
+          <t>Livvika, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598950</v>
+        <v>599006</v>
       </c>
       <c r="R2" t="n">
-        <v>6853474</v>
+        <v>6853483</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,66 +780,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113650399</v>
+        <v>89522804</v>
       </c>
       <c r="B3" t="n">
-        <v>56231</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Överbyn, Hls</t>
+          <t>Rövarklitten, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598983</v>
+        <v>599063</v>
       </c>
       <c r="R3" t="n">
-        <v>6853490</v>
+        <v>6853561</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,34 +859,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elsa Scharin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elsa Scharin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119697323</v>
+        <v>113650448</v>
       </c>
       <c r="B4" t="n">
-        <v>90606</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,41 +892,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>100137</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Livvika, Hls</t>
+          <t>Överbyn, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599006</v>
+        <v>598922</v>
       </c>
       <c r="R4" t="n">
-        <v>6853483</v>
+        <v>6853444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,12 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,19 +964,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lena Scharin</t>
+          <t>Elsa Scharin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lena Scharin</t>
+          <t>Elsa Scharin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,16 +985,11 @@
         <v>122272418</v>
       </c>
       <c r="B5" t="n">
-        <v>57334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1137,6 +1098,227 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113650399</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Överbyn, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598983</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6853490</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elsa Scharin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elsa Scharin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112510635</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Livvika, Dånsjön, Forsa, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6853474</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lena Scharin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lena Scharin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
